--- a/public/exports/29189978.xlsx
+++ b/public/exports/29189978.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294470</t>
+          <t xml:space="preserve">311294471</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294461</t>
+          <t xml:space="preserve">311294465</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">

--- a/public/exports/29189978.xlsx
+++ b/public/exports/29189978.xlsx
@@ -7114,7 +7114,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294471</t>
+          <t xml:space="preserve">311294470</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294465</t>
+          <t xml:space="preserve">311294461</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
